--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0DE180E-F472-4BDC-81A8-89A06C81F1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4837C317-02B8-4659-ABCE-0B66EAC617AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -528,11 +528,101 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -549,101 +639,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,82 +1026,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="47" t="s">
+      <c r="A1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="49"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="55"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40"/>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="44" t="s">
+      <c r="A2" s="46"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="46"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="50" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="58"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="53" t="s">
+      <c r="A4" s="48"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="54"/>
-      <c r="I4" s="54"/>
-      <c r="J4" s="55"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="61"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="56" t="s">
+      <c r="A5" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="58"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="61" t="s">
+      <c r="A6" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="20"/>
@@ -1112,11 +1112,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="59"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1126,11 +1126,11 @@
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="59"/>
-      <c r="C8" s="59"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
@@ -1143,11 +1143,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="60" t="s">
+      <c r="A9" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="60"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1191,19 +1191,19 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32">
+      <c r="A11" s="62">
         <v>1</v>
       </c>
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="65" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -1225,11 +1225,11 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="36"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="66"/>
       <c r="F12" s="15" t="s">
         <v>37</v>
       </c>
@@ -1252,10 +1252,10 @@
       <c r="A13" s="29">
         <v>2</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="68" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -1286,10 +1286,10 @@
       <c r="A14" s="29">
         <v>3</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="67" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="68" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -1317,18 +1317,18 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62" t="s">
+      <c r="A15" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="64"/>
-      <c r="J15" s="68">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="30">
         <f>SUM(J11:J14)</f>
         <v>1420000</v>
       </c>
@@ -1361,37 +1361,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="66" t="s">
+      <c r="A18" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="66"/>
-      <c r="C18" s="66"/>
-      <c r="D18" s="66"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
       <c r="E18" s="9"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="67" t="s">
+      <c r="A19" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
       <c r="E19" s="11"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="67" t="s">
+      <c r="G19" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="67"/>
-      <c r="I19" s="67"/>
-      <c r="J19" s="67"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="36"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1462,20 +1462,20 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="65" t="s">
+      <c r="A25" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="65"/>
-      <c r="D25" s="65"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
       <c r="E25" s="10"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="65" t="s">
+      <c r="G25" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="65"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="65"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
       <c r="K25" s="16"/>
       <c r="AA25" s="2"/>
     </row>
@@ -1553,6 +1553,21 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="22">
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A18:D18"/>
@@ -1560,21 +1575,6 @@
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G25:J25"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4837C317-02B8-4659-ABCE-0B66EAC617AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76E5E0D-554C-4EDA-A942-0446908E1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -443,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -531,6 +531,12 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -639,11 +645,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1026,82 +1029,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43"/>
-      <c r="B1" s="44"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="53" t="s">
+      <c r="A1" s="45"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="55"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="50" t="s">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="52"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="46"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="56" t="s">
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="58"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="60"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="59" t="s">
+      <c r="A4" s="50"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="61"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="63"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="41"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="42"/>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="20"/>
@@ -1112,11 +1115,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1126,11 +1129,11 @@
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
+      <c r="A8" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
@@ -1143,11 +1146,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1191,19 +1194,19 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62">
+      <c r="A11" s="64">
         <v>1</v>
       </c>
-      <c r="B11" s="62" t="s">
+      <c r="B11" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="62" t="s">
+      <c r="C11" s="64" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="65" t="s">
+      <c r="E11" s="67" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -1225,11 +1228,11 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="63"/>
-      <c r="B12" s="64"/>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="66"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="66"/>
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="68"/>
       <c r="F12" s="15" t="s">
         <v>37</v>
       </c>
@@ -1252,10 +1255,10 @@
       <c r="A13" s="29">
         <v>2</v>
       </c>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="68" t="s">
+      <c r="C13" s="32" t="s">
         <v>32</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -1286,10 +1289,10 @@
       <c r="A14" s="29">
         <v>3</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="68" t="s">
+      <c r="C14" s="32" t="s">
         <v>33</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -1317,17 +1320,17 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="35"/>
       <c r="J15" s="30">
         <f>SUM(J11:J14)</f>
         <v>1420000</v>
@@ -1361,37 +1364,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="9"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="35" t="s">
+      <c r="G18" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="35"/>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
       <c r="E19" s="11"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1404,7 +1407,10 @@
       <c r="G20" s="27"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="26"/>
+      <c r="J20" s="69">
+        <f>SUM(J11:J12)</f>
+        <v>1020000</v>
+      </c>
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1462,20 +1468,20 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
+      <c r="B25" s="36"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="10"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="34" t="s">
+      <c r="G25" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
       <c r="K25" s="16"/>
       <c r="AA25" s="2"/>
     </row>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 03/01. Báo giá bảo hành/BG_AnhTuanBG_200326.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 03\01. Báo giá bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76E5E0D-554C-4EDA-A942-0446908E1BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCC22E0-9058-4DC9-BD50-7CE50F7C493C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -537,6 +537,99 @@
     <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -553,99 +646,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1029,82 +1029,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="51"/>
     </row>
     <row r="2" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="52" t="s">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="54"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="48"/>
     </row>
     <row r="3" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="58" t="s">
+      <c r="A3" s="42"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="59"/>
-      <c r="I3" s="59"/>
-      <c r="J3" s="60"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="54"/>
     </row>
     <row r="4" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="50"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="61" t="s">
+      <c r="A4" s="44"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:27" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="40"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="60"/>
     </row>
     <row r="6" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="20"/>
@@ -1115,11 +1115,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="61"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1129,11 +1129,11 @@
       <c r="J7" s="11"/>
     </row>
     <row r="8" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8" t="s">
@@ -1146,11 +1146,11 @@
       <c r="AA8" s="2"/>
     </row>
     <row r="9" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1194,19 +1194,19 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="64">
+      <c r="A11" s="34">
         <v>1</v>
       </c>
-      <c r="B11" s="64" t="s">
+      <c r="B11" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="64" t="s">
+      <c r="C11" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="64" t="s">
+      <c r="D11" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="37" t="s">
         <v>30</v>
       </c>
       <c r="F11" s="15" t="s">
@@ -1228,11 +1228,11 @@
       <c r="AA11" s="2"/>
     </row>
     <row r="12" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="65"/>
-      <c r="B12" s="66"/>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="68"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="15" t="s">
         <v>37</v>
       </c>
@@ -1320,17 +1320,17 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="35"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="66"/>
       <c r="J15" s="30">
         <f>SUM(J11:J14)</f>
         <v>1420000</v>
@@ -1364,37 +1364,37 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
+      <c r="A18" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
       <c r="E18" s="9"/>
       <c r="F18" s="19"/>
-      <c r="G18" s="37" t="s">
+      <c r="G18" s="68" t="s">
         <v>16</v>
       </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="38"/>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
       <c r="E19" s="11"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1407,10 +1407,7 @@
       <c r="G20" s="27"/>
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="69">
-        <f>SUM(J11:J12)</f>
-        <v>1020000</v>
-      </c>
+      <c r="J20" s="33"/>
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1468,20 +1465,20 @@
       <c r="AA24" s="2"/>
     </row>
     <row r="25" spans="1:27" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="36"/>
-      <c r="D25" s="36"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
       <c r="E25" s="10"/>
       <c r="F25" s="16"/>
-      <c r="G25" s="36" t="s">
+      <c r="G25" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="67"/>
+      <c r="J25" s="67"/>
       <c r="K25" s="16"/>
       <c r="AA25" s="2"/>
     </row>
@@ -1559,21 +1556,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="22">
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D1:J1"/>
-    <mergeCell ref="D3:J3"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A18:D18"/>
@@ -1581,6 +1563,21 @@
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="G25:J25"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D1:J1"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D4" r:id="rId1" display="http://vnetgps.vn" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
